--- a/posicoes/Contas.xlsx
+++ b/posicoes/Contas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B269B1F-FC3A-424E-8B34-D2A24AB9FCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE83CDD-7505-4EDD-88E8-0E8C8B7D4C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="-16440" windowWidth="29040" windowHeight="15840" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
   </bookViews>
@@ -30,9 +30,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="287">
   <si>
-    <t>NÚMERO DA CONTA</t>
-  </si>
-  <si>
     <t>CLIENTE</t>
   </si>
   <si>
@@ -888,7 +885,10 @@
     <t>GRUPO GERAL</t>
   </si>
   <si>
-    <t>CORRETORA</t>
+    <t>corretora</t>
+  </si>
+  <si>
+    <t>conta</t>
   </si>
 </sst>
 </file>
@@ -1291,3695 +1291,3695 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>3</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3">
         <v>2729546</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" s="3">
         <v>5166121</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3">
         <v>5370995</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3">
         <v>2123318</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3">
         <v>6703116</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3">
         <v>2027022</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3">
         <v>19301650</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3">
         <v>35704002</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3">
         <v>3082235</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3">
         <v>23572514</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="3">
         <v>7153570</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" s="3">
         <v>53076915</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="3">
         <v>6445064</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3">
         <v>7161258</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" s="3">
         <v>27109027</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" s="3">
         <v>12255170</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="3">
         <v>23546070</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" s="3">
         <v>98792193</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" s="3">
         <v>3246094</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>19003827</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="3">
         <v>11370136</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" s="3">
         <v>2045140</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E25" s="3">
         <v>63338577</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="3">
         <v>23314990</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" s="3">
         <v>17736177</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="3">
         <v>20045904</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" s="3">
         <v>3630513</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E30" s="3">
         <v>73800696</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E31" s="3">
         <v>83075437</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="3">
         <v>500819</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33" s="3">
         <v>4498022</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="3">
         <v>3721574</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E35" s="3">
         <v>83140110</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="3">
         <v>17208214</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" s="3">
         <v>15706583</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="3">
         <v>11948279</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E39" s="3">
         <v>51121087</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" s="3">
         <v>2408885</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="3">
         <v>4760422</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="3">
         <v>6860829</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" s="3">
         <v>3004033</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" s="3">
         <v>9317618</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="3">
         <v>576471</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E46" s="3">
         <v>76519394</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="3">
         <v>7777265</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E48" s="3">
         <v>23147291</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="3">
         <v>19251578</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E50" s="3">
         <v>23638180</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" s="3">
         <v>7983962</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52" s="3">
         <v>3686769</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E53" s="3">
         <v>339991</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E54" s="3">
         <v>61663347</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E55" s="3">
         <v>11466830</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E56" s="3">
         <v>13759983</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E57" s="3">
         <v>6703094</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E58" s="3">
         <v>6696173</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E59" s="3">
         <v>21272927</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E60" s="3">
         <v>17624003</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E61" s="3">
         <v>2758096</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E62" s="3">
         <v>79451840</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E63" s="3">
         <v>2497441</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64" s="3">
         <v>3133112</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E65" s="3">
         <v>87523267</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E66" s="3">
         <v>92343302</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E67" s="3">
         <v>7758450</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E68" s="3">
         <v>14668131</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E69" s="3">
         <v>17789609</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E70" s="3">
         <v>67227652</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E71" s="3">
         <v>3371553</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E72" s="3">
         <v>4619413</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E73" s="3">
         <v>5949720</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D74" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E74" s="3">
         <v>10800085</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E75" s="3">
         <v>25968661</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E76" s="3">
         <v>4252546</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E77" s="3">
         <v>3101560</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E78" s="3">
         <v>22391056</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E79" s="3">
         <v>65431389</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E80" s="3">
         <v>98061659</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E81" s="3">
         <v>18129345</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="F82" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E83" s="3">
         <v>4718691</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E84" s="3">
         <v>2068296</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E85" s="3">
         <v>6700800</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E86" s="3">
         <v>4771941</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D87" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E87" s="3">
         <v>4475136</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D88" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E88" s="3">
         <v>32892096</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E89" s="3">
         <v>4474935</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E90" s="3">
         <v>2063235</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I90" s="1"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D91" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E91" s="3">
         <v>19515384</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E92" s="3">
         <v>29206363</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E93" s="3">
         <v>36200373</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E94" s="3">
         <v>3208501</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E95" s="3">
         <v>483586</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E96" s="3">
         <v>6703078</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E97" s="3">
         <v>391189</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E98" s="3">
         <v>5541778</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D99" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E99" s="3">
         <v>2912475</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E100" s="3">
         <v>1959557</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E101" s="3">
         <v>78224399</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E102" s="3">
         <v>3997766</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E103" s="3">
         <v>19597273</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E104" s="3">
         <v>61160053</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E105" s="3">
         <v>18850870</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E106" s="3">
         <v>58792416</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E107" s="3">
         <v>71802417</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E108" s="3">
         <v>20082148</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E109" s="3">
         <v>292615</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E110" s="3">
         <v>18818976</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E111" s="3">
         <v>11210659</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E112" s="3">
         <v>95396715</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E113" s="3">
         <v>579979</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E114" s="3">
         <v>35318483</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E115" s="3">
         <v>2247004</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D116" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E116" s="3">
         <v>242411</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E117" s="3">
         <v>4164584</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E118" s="3">
         <v>64343370</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E119" s="3">
         <v>16917348</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B120" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C120" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D120" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E120" s="3">
         <v>16424007</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E121" s="3">
         <v>85021853</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B122" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C122" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D122" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E122" s="3">
         <v>19657497</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E123" s="3">
         <v>9248969</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C124" s="3"/>
       <c r="D124" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E124" s="3">
         <v>2067728</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E125" s="3">
         <v>52778847</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C126" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D126" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E126" s="3">
         <v>598451</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C127" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D127" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E127" s="3">
         <v>68501</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E128" s="3">
         <v>4466342</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B129" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C129" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D129" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E129" s="3">
         <v>17866382</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K129" s="4"/>
       <c r="L129" s="4"/>
@@ -12263,31 +12263,31 @@
     </row>
     <row r="130" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B130" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C130" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D130" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E130" s="3">
         <v>7272031</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K130" s="4"/>
       <c r="L130" s="4"/>
@@ -19571,304 +19571,304 @@
     </row>
     <row r="131" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="132" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E132" s="3">
         <v>26245282</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G132" s="1"/>
       <c r="H132" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E133" s="3">
         <v>3093727</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G133" s="1"/>
       <c r="H133" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E134" s="3">
         <v>14918710</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E135" s="3">
         <v>9445242</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E136" s="3">
         <v>3588879</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G136" s="1"/>
       <c r="H136" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E137" s="3">
         <v>18466421</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G137" s="1"/>
       <c r="H137" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E138" s="3">
         <v>19082129</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G138" s="1"/>
       <c r="H138" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E139" s="3">
         <v>17770891</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G139" s="1"/>
       <c r="H139" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E140" s="3">
         <v>4163084</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G140" s="1"/>
       <c r="H140" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="141" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E141" s="3">
         <v>19522034</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G141" s="1"/>
       <c r="H141" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I141" s="1"/>
     </row>
     <row r="142" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E142" s="3">
         <v>3257275</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/posicoes/Contas.xlsx
+++ b/posicoes/Contas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE83CDD-7505-4EDD-88E8-0E8C8B7D4C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2164E288-11E5-40C2-9546-9FC897A0A87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="-16440" windowWidth="29040" windowHeight="15840" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
   </bookViews>
@@ -1431,8 +1431,8 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>41</v>
+      <c r="A6" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>29</v>
@@ -1458,8 +1458,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>41</v>
+      <c r="A7" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
@@ -1485,8 +1485,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>41</v>
+      <c r="A8" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
@@ -1947,8 +1947,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>41</v>
+      <c r="A24" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>29</v>
@@ -3843,8 +3843,8 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>41</v>
+      <c r="A90" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>29</v>
@@ -3984,8 +3984,8 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>41</v>
+      <c r="A95" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>30</v>
@@ -4011,8 +4011,8 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>41</v>
+      <c r="A96" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>29</v>
@@ -4038,8 +4038,8 @@
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>41</v>
+      <c r="A97" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>29</v>
@@ -4065,8 +4065,8 @@
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>41</v>
+      <c r="A98" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>29</v>

--- a/posicoes/Contas.xlsx
+++ b/posicoes/Contas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Aplicativo Alocação\posicoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2164E288-11E5-40C2-9546-9FC897A0A87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE6D978-1EA8-4B3A-9766-83F039798CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="-16440" windowWidth="29040" windowHeight="15840" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$I$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$I$142</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="287">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -939,7 +939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -952,10 +952,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1290,31 +1286,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1428,10 +1424,12 @@
       <c r="H5" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1458,7 +1456,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1485,7 +1483,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1947,7 +1945,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -3843,7 +3841,7 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="1" t="s">
         <v>141</v>
       </c>
       <c r="B90" s="3" t="s">
@@ -3984,7 +3982,7 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B95" s="3" t="s">
@@ -4011,7 +4009,7 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B96" s="3" t="s">
@@ -4038,7 +4036,7 @@
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -4065,7 +4063,7 @@
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B98" s="3" t="s">
@@ -19872,6 +19870,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I142" xr:uid="{9DB8E20E-57E2-4347-94BA-5457C4460B8B}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/posicoes/Contas.xlsx
+++ b/posicoes/Contas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Aplicativo Alocação\posicoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE6D978-1EA8-4B3A-9766-83F039798CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96273054-1583-4AB3-8E16-91684D42AEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="-16440" windowWidth="29040" windowHeight="15840" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="286">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -151,9 +151,6 @@
   </si>
   <si>
     <t>Fabricio Franco Naves</t>
-  </si>
-  <si>
-    <t>Família D Alessandro</t>
   </si>
   <si>
     <t>Iolivan Jose de Brito</t>
@@ -1287,7 +1284,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>27</v>
@@ -1296,10 +1293,10 @@
         <v>28</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -1337,7 +1334,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>20</v>
@@ -1360,13 +1357,13 @@
         <v>5166121</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>32</v>
@@ -1389,13 +1386,13 @@
         <v>5370995</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>20</v>
@@ -1403,7 +1400,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>29</v>
@@ -1416,13 +1413,13 @@
         <v>2123318</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>23</v>
@@ -1430,7 +1427,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>29</v>
@@ -1443,13 +1440,13 @@
         <v>6703116</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>20</v>
@@ -1457,7 +1454,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>29</v>
@@ -1470,13 +1467,13 @@
         <v>2027022</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>20</v>
@@ -1484,26 +1481,26 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>20</v>
@@ -1511,7 +1508,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>30</v>
@@ -1526,13 +1523,13 @@
         <v>19301650</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>25</v>
@@ -1540,7 +1537,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>30</v>
@@ -1555,13 +1552,13 @@
         <v>35704002</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>7</v>
@@ -1569,7 +1566,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>30</v>
@@ -1584,13 +1581,13 @@
         <v>3082235</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>20</v>
@@ -1598,7 +1595,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>29</v>
@@ -1613,13 +1610,13 @@
         <v>23572514</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>32</v>
@@ -1627,7 +1624,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>29</v>
@@ -1642,7 +1639,7 @@
         <v>7153570</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>10</v>
@@ -1677,7 +1674,7 @@
         <v>10</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>7</v>
@@ -1700,13 +1697,13 @@
         <v>6445064</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>7</v>
@@ -1735,7 +1732,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>24</v>
@@ -1743,7 +1740,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
@@ -1758,13 +1755,13 @@
         <v>27109027</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>7</v>
@@ -1772,7 +1769,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>29</v>
@@ -1787,13 +1784,13 @@
         <v>12255170</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>7</v>
@@ -1801,7 +1798,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>29</v>
@@ -1816,13 +1813,13 @@
         <v>23546070</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>7</v>
@@ -1830,7 +1827,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>29</v>
@@ -1845,13 +1842,13 @@
         <v>98792193</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>7</v>
@@ -1859,7 +1856,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
@@ -1874,13 +1871,13 @@
         <v>3246094</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>20</v>
@@ -1888,7 +1885,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>29</v>
@@ -1903,13 +1900,13 @@
         <v>19003827</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>20</v>
@@ -1932,13 +1929,13 @@
         <v>11370136</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>32</v>
@@ -1946,7 +1943,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>29</v>
@@ -1959,19 +1956,19 @@
         <v>2045140</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>29</v>
@@ -1986,13 +1983,13 @@
         <v>63338577</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>32</v>
@@ -2000,7 +1997,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>29</v>
@@ -2015,13 +2012,13 @@
         <v>23314990</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>32</v>
@@ -2029,7 +2026,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>29</v>
@@ -2044,13 +2041,13 @@
         <v>17736177</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>22</v>
@@ -2058,7 +2055,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>29</v>
@@ -2071,19 +2068,19 @@
         <v>20045904</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>29</v>
@@ -2098,13 +2095,13 @@
         <v>3630513</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>21</v>
@@ -2112,7 +2109,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>29</v>
@@ -2127,13 +2124,13 @@
         <v>73800696</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>21</v>
@@ -2141,7 +2138,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>29</v>
@@ -2156,13 +2153,13 @@
         <v>83075437</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>21</v>
@@ -2170,7 +2167,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>30</v>
@@ -2185,13 +2182,13 @@
         <v>500819</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>21</v>
@@ -2220,7 +2217,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>20</v>
@@ -2249,7 +2246,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>20</v>
@@ -2257,7 +2254,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>30</v>
@@ -2272,13 +2269,13 @@
         <v>83140110</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>22</v>
@@ -2286,7 +2283,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>30</v>
@@ -2301,13 +2298,13 @@
         <v>17208214</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>22</v>
@@ -2315,7 +2312,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>30</v>
@@ -2330,13 +2327,13 @@
         <v>15706583</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>22</v>
@@ -2344,7 +2341,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>29</v>
@@ -2359,13 +2356,13 @@
         <v>11948279</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>22</v>
@@ -2373,7 +2370,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>30</v>
@@ -2388,13 +2385,13 @@
         <v>51121087</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>20</v>
@@ -2402,7 +2399,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>29</v>
@@ -2417,13 +2414,13 @@
         <v>2408885</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>20</v>
@@ -2431,7 +2428,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>29</v>
@@ -2446,13 +2443,13 @@
         <v>4760422</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>23</v>
@@ -2460,7 +2457,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>29</v>
@@ -2475,13 +2472,13 @@
         <v>6860829</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>20</v>
@@ -2489,7 +2486,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>29</v>
@@ -2504,13 +2501,13 @@
         <v>3004033</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>20</v>
@@ -2518,7 +2515,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>29</v>
@@ -2533,13 +2530,13 @@
         <v>9317618</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>32</v>
@@ -2547,7 +2544,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>29</v>
@@ -2562,19 +2559,19 @@
         <v>576471</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>29</v>
@@ -2589,19 +2586,19 @@
         <v>76519394</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>29</v>
@@ -2616,13 +2613,13 @@
         <v>7777265</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>24</v>
@@ -2630,7 +2627,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>29</v>
@@ -2645,13 +2642,13 @@
         <v>23147291</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>25</v>
@@ -2659,7 +2656,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>29</v>
@@ -2674,13 +2671,13 @@
         <v>19251578</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>25</v>
@@ -2688,7 +2685,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>29</v>
@@ -2703,13 +2700,13 @@
         <v>23638180</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>25</v>
@@ -2732,13 +2729,13 @@
         <v>7983962</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>32</v>
@@ -2746,7 +2743,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>29</v>
@@ -2761,13 +2758,13 @@
         <v>3686769</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>25</v>
@@ -2802,7 +2799,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>29</v>
@@ -2817,13 +2814,13 @@
         <v>61663347</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>24</v>
@@ -2831,7 +2828,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>30</v>
@@ -2846,13 +2843,13 @@
         <v>11466830</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>24</v>
@@ -2860,7 +2857,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>30</v>
@@ -2869,19 +2866,19 @@
         <v>30</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E56" s="3">
         <v>13759983</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>24</v>
@@ -2889,7 +2886,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>29</v>
@@ -2904,13 +2901,13 @@
         <v>6703094</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>24</v>
@@ -2918,7 +2915,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>29</v>
@@ -2933,13 +2930,13 @@
         <v>6696173</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>24</v>
@@ -2947,7 +2944,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>29</v>
@@ -2962,13 +2959,13 @@
         <v>21272927</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>32</v>
@@ -2976,7 +2973,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>29</v>
@@ -2991,13 +2988,13 @@
         <v>17624003</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>22</v>
@@ -3005,7 +3002,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>29</v>
@@ -3020,13 +3017,13 @@
         <v>2758096</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>21</v>
@@ -3034,7 +3031,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>29</v>
@@ -3049,13 +3046,13 @@
         <v>79451840</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>21</v>
@@ -3063,7 +3060,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>29</v>
@@ -3078,13 +3075,13 @@
         <v>2497441</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>21</v>
@@ -3092,7 +3089,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>29</v>
@@ -3107,13 +3104,13 @@
         <v>3133112</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>24</v>
@@ -3121,7 +3118,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>30</v>
@@ -3136,13 +3133,13 @@
         <v>87523267</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>22</v>
@@ -3150,7 +3147,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>30</v>
@@ -3171,7 +3168,7 @@
         <v>10</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>22</v>
@@ -3179,7 +3176,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>29</v>
@@ -3194,13 +3191,13 @@
         <v>7758450</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>22</v>
@@ -3208,7 +3205,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>29</v>
@@ -3223,11 +3220,11 @@
         <v>14668131</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>22</v>
@@ -3235,7 +3232,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>29</v>
@@ -3256,7 +3253,7 @@
         <v>10</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>22</v>
@@ -3264,7 +3261,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>29</v>
@@ -3279,13 +3276,13 @@
         <v>67227652</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>22</v>
@@ -3293,7 +3290,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>29</v>
@@ -3308,13 +3305,13 @@
         <v>3371553</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>22</v>
@@ -3322,7 +3319,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>29</v>
@@ -3337,13 +3334,13 @@
         <v>4619413</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>22</v>
@@ -3351,7 +3348,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>29</v>
@@ -3366,13 +3363,13 @@
         <v>5949720</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>7</v>
@@ -3380,7 +3377,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>29</v>
@@ -3395,13 +3392,13 @@
         <v>10800085</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>7</v>
@@ -3409,26 +3406,26 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E75" s="3">
         <v>25968661</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>24</v>
@@ -3436,7 +3433,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>29</v>
@@ -3451,13 +3448,13 @@
         <v>4252546</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>24</v>
@@ -3465,7 +3462,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>29</v>
@@ -3480,13 +3477,13 @@
         <v>3101560</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>24</v>
@@ -3494,7 +3491,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>29</v>
@@ -3509,13 +3506,13 @@
         <v>22391056</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>22</v>
@@ -3523,7 +3520,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>29</v>
@@ -3538,13 +3535,13 @@
         <v>65431389</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>22</v>
@@ -3552,7 +3549,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>29</v>
@@ -3567,13 +3564,13 @@
         <v>98061659</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>22</v>
@@ -3581,7 +3578,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>29</v>
@@ -3596,13 +3593,13 @@
         <v>18129345</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>22</v>
@@ -3610,7 +3607,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>29</v>
@@ -3625,13 +3622,13 @@
         <v>35</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>22</v>
@@ -3639,7 +3636,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>29</v>
@@ -3654,13 +3651,13 @@
         <v>4718691</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>21</v>
@@ -3668,7 +3665,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>29</v>
@@ -3683,13 +3680,13 @@
         <v>2068296</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>21</v>
@@ -3697,7 +3694,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>29</v>
@@ -3712,13 +3709,13 @@
         <v>6700800</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>24</v>
@@ -3726,7 +3723,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>30</v>
@@ -3741,13 +3738,13 @@
         <v>4771941</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>24</v>
@@ -3755,7 +3752,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>29</v>
@@ -3770,13 +3767,13 @@
         <v>4475136</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>32</v>
@@ -3784,7 +3781,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>29</v>
@@ -3813,7 +3810,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>29</v>
@@ -3828,13 +3825,13 @@
         <v>4474935</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>32</v>
@@ -3842,7 +3839,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>29</v>
@@ -3855,19 +3852,19 @@
         <v>2063235</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I90" s="1"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>29</v>
@@ -3882,13 +3879,13 @@
         <v>19515384</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>7</v>
@@ -3896,7 +3893,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>29</v>
@@ -3911,13 +3908,13 @@
         <v>29206363</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>20</v>
@@ -3925,7 +3922,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>29</v>
@@ -3946,7 +3943,7 @@
         <v>9</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>20</v>
@@ -3954,7 +3951,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>29</v>
@@ -3969,13 +3966,13 @@
         <v>3208501</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>20</v>
@@ -3983,7 +3980,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>30</v>
@@ -3996,13 +3993,13 @@
         <v>483586</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>23</v>
@@ -4010,7 +4007,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>29</v>
@@ -4023,13 +4020,13 @@
         <v>6703078</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>23</v>
@@ -4037,7 +4034,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>29</v>
@@ -4050,13 +4047,13 @@
         <v>391189</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>23</v>
@@ -4064,7 +4061,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>29</v>
@@ -4077,13 +4074,13 @@
         <v>5541778</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>23</v>
@@ -4091,7 +4088,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>29</v>
@@ -4106,13 +4103,13 @@
         <v>2912475</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>20</v>
@@ -4120,7 +4117,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>30</v>
@@ -4135,13 +4132,13 @@
         <v>1959557</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>21</v>
@@ -4149,7 +4146,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>30</v>
@@ -4164,13 +4161,13 @@
         <v>78224399</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>21</v>
@@ -4178,7 +4175,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>30</v>
@@ -4193,13 +4190,13 @@
         <v>3997766</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>21</v>
@@ -4207,7 +4204,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>30</v>
@@ -4220,13 +4217,13 @@
         <v>19597273</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>32</v>
@@ -4234,7 +4231,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>30</v>
@@ -4249,13 +4246,13 @@
         <v>61160053</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>25</v>
@@ -4263,7 +4260,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>30</v>
@@ -4278,13 +4275,13 @@
         <v>18850870</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>25</v>
@@ -4292,7 +4289,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>30</v>
@@ -4307,13 +4304,13 @@
         <v>58792416</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>25</v>
@@ -4321,7 +4318,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>30</v>
@@ -4342,7 +4339,7 @@
         <v>9</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>21</v>
@@ -4350,7 +4347,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>30</v>
@@ -4365,13 +4362,13 @@
         <v>20082148</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>21</v>
@@ -4379,7 +4376,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>30</v>
@@ -4394,13 +4391,13 @@
         <v>292615</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>21</v>
@@ -4408,7 +4405,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>29</v>
@@ -4423,13 +4420,13 @@
         <v>18818976</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>21</v>
@@ -4437,7 +4434,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>30</v>
@@ -4452,13 +4449,13 @@
         <v>11210659</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>23</v>
@@ -4466,7 +4463,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>29</v>
@@ -4481,13 +4478,13 @@
         <v>95396715</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>20</v>
@@ -4495,7 +4492,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>30</v>
@@ -4510,13 +4507,13 @@
         <v>579979</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>20</v>
@@ -4524,7 +4521,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>29</v>
@@ -4539,13 +4536,13 @@
         <v>35318483</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>26</v>
@@ -4553,7 +4550,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>29</v>
@@ -4568,11 +4565,11 @@
         <v>2247004</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>26</v>
@@ -4580,7 +4577,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>29</v>
@@ -4595,13 +4592,13 @@
         <v>242411</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>32</v>
@@ -4609,7 +4606,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>29</v>
@@ -4624,13 +4621,13 @@
         <v>4164584</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>20</v>
@@ -4638,7 +4635,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>30</v>
@@ -4653,13 +4650,13 @@
         <v>64343370</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>20</v>
@@ -4667,7 +4664,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>29</v>
@@ -4682,13 +4679,13 @@
         <v>16917348</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>20</v>
@@ -4696,7 +4693,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>29</v>
@@ -4711,13 +4708,13 @@
         <v>16424007</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>32</v>
@@ -4725,7 +4722,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>29</v>
@@ -4740,13 +4737,13 @@
         <v>85021853</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>7</v>
@@ -4754,7 +4751,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>29</v>
@@ -4769,13 +4766,13 @@
         <v>19657497</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>32</v>
@@ -4783,7 +4780,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>30</v>
@@ -4798,11 +4795,11 @@
         <v>9248969</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>32</v>
@@ -4810,7 +4807,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>29</v>
@@ -4823,13 +4820,13 @@
         <v>2067728</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>20</v>
@@ -4837,7 +4834,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>29</v>
@@ -4852,13 +4849,13 @@
         <v>52778847</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>24</v>
@@ -4866,7 +4863,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>29</v>
@@ -4881,13 +4878,13 @@
         <v>598451</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>24</v>
@@ -4895,7 +4892,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>29</v>
@@ -4910,13 +4907,13 @@
         <v>68501</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>24</v>
@@ -4924,7 +4921,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>30</v>
@@ -4939,13 +4936,13 @@
         <v>4466342</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>23</v>
@@ -4953,7 +4950,7 @@
     </row>
     <row r="129" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>29</v>
@@ -4968,13 +4965,13 @@
         <v>17866382</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>22</v>
@@ -12261,7 +12258,7 @@
     </row>
     <row r="130" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>29</v>
@@ -12276,13 +12273,13 @@
         <v>7272031</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>22</v>
@@ -19569,7 +19566,7 @@
     </row>
     <row r="131" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>30</v>
@@ -19578,27 +19575,27 @@
         <v>30</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="132" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3" t="s">
@@ -19611,11 +19608,11 @@
         <v>26245282</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G132" s="1"/>
       <c r="H132" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>20</v>
@@ -19623,7 +19620,7 @@
     </row>
     <row r="133" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3" t="s">
@@ -19636,11 +19633,11 @@
         <v>3093727</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G133" s="1"/>
       <c r="H133" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>20</v>
@@ -19686,11 +19683,11 @@
         <v>9445242</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>32</v>
@@ -19698,7 +19695,7 @@
     </row>
     <row r="136" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3" t="s">
@@ -19711,11 +19708,11 @@
         <v>3588879</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G136" s="1"/>
       <c r="H136" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>24</v>
@@ -19736,11 +19733,11 @@
         <v>18466421</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G137" s="1"/>
       <c r="H137" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>32</v>
@@ -19748,7 +19745,7 @@
     </row>
     <row r="138" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3" t="s">
@@ -19761,11 +19758,11 @@
         <v>19082129</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G138" s="1"/>
       <c r="H138" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>23</v>
@@ -19773,7 +19770,7 @@
     </row>
     <row r="139" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
@@ -19786,11 +19783,11 @@
         <v>17770891</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G139" s="1"/>
       <c r="H139" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>32</v>
@@ -19811,11 +19808,11 @@
         <v>4163084</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G140" s="1"/>
       <c r="H140" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>32</v>
@@ -19823,7 +19820,7 @@
     </row>
     <row r="141" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
@@ -19836,17 +19833,17 @@
         <v>19522034</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G141" s="1"/>
       <c r="H141" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I141" s="1"/>
     </row>
     <row r="142" spans="1:1022 1028:2048 2054:4091 4097:5117 5123:6143 6149:9212 9218:10238 10244:11264 11270:13307 13313:14333 14339:15359 15365:16384" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3" t="s">
@@ -19859,11 +19856,11 @@
         <v>3257275</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>20</v>
